--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MARISTAS VALENCIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MARISTAS VALENCIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. LEMISHKA</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>29.9793</v>
+        <v>20.4497</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1339</v>
+        <v>20.4497</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8455</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>14.5082</v>
+        <v>20.4497</v>
       </c>
       <c r="H2" t="n">
-        <v>11.5103</v>
+        <v>14.8972</v>
       </c>
       <c r="I2" t="n">
-        <v>2.997899999999999</v>
+        <v>5.5529</v>
       </c>
       <c r="J2" t="n">
-        <v>15.3445</v>
+        <v>20.4497</v>
       </c>
       <c r="K2" t="n">
-        <v>14.8393</v>
+        <v>14.8972</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5052999999999996</v>
+        <v>5.5529</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8364000000000003</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.3289</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4926</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-11.5107</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-25.0971</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>13.5864</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>12.8307</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>16.3692</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.218300000000001</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>7.055400000000001</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.2737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>V. LEMISHKA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>20.4497</v>
+        <v>15.1175</v>
       </c>
       <c r="E3" t="n">
-        <v>20.4497</v>
+        <v>2.3624</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>12.755</v>
       </c>
       <c r="G3" t="n">
-        <v>20.4497</v>
+        <v>14.5082</v>
       </c>
       <c r="H3" t="n">
-        <v>14.8972</v>
+        <v>11.5103</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5529</v>
+        <v>2.997899999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>20.4497</v>
+        <v>15.3445</v>
       </c>
       <c r="K3" t="n">
-        <v>14.8972</v>
+        <v>14.8393</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5529</v>
+        <v>0.5052999999999996</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.8364000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-3.3289</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.4926</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-11.5107</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-25.0971</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>13.5864</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>14.3383</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>5.0594</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>9.2788</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-2.218300000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>7.055400000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-9.2737</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>V. AVIÑO ESPAÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8.3048</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>9.6661</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3612</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8957000000000007</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9649</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0695</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>15.7466</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>13.5739</v>
+        <v>0.9509000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1729</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.8508</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.6087</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.2422</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.2079</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-30.0033</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>26.7954</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>19.2459</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18.8111</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4348000000000001</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-8.629000000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>5.1116</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.7406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>J. GIL SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.004999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.980000000000002</v>
+        <v>0.0974</v>
       </c>
       <c r="F6" t="n">
-        <v>7.984999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="G6" t="n">
-        <v>-13.2241</v>
+        <v>0.1299</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3409</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.5648</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>12.7018</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>22.7655</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.0636</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-25.926</v>
+        <v>0.1299</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.4248</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.5012</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>6.2271</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-39.627</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>45.8541</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>14.5238</v>
+        <v>0.1415</v>
       </c>
       <c r="T6" t="n">
-        <v>4.7601</v>
+        <v>0.0974</v>
       </c>
       <c r="U6" t="n">
-        <v>9.763400000000001</v>
+        <v>0.0441</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5218</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>19.1847</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.7065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. AVIÑO ESPAÑA</t>
+          <t>D. ANGELES SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9509000000000001</v>
+        <v>1.6255</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.4995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.7489</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.6731</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9509000000000001</v>
+        <v>1.4568</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9509000000000001</v>
+        <v>1.4157</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.381</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.7143</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.3518</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0555</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2963</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GIL SANCHEZ</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1475</v>
+        <v>-0.4242000000000008</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-6.146799999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1475</v>
+        <v>5.722499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1299</v>
+        <v>-13.2241</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4.3409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1299</v>
+        <v>-17.5648</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>12.7018</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>22.7655</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-10.0636</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1299</v>
+        <v>-25.926</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-18.4248</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1299</v>
+        <v>-7.5012</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.2271</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-39.627</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>45.8541</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0176</v>
+        <v>9.094099999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.593</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0176</v>
+        <v>7.5014</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.5218</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>19.1847</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-21.7065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ANGELES SANCHEZ</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5968</v>
+        <v>-1.811200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9821</v>
+        <v>-1.0855</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5789</v>
+        <v>-0.7258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.8957000000000007</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7489</v>
+        <v>1.9649</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6731</v>
+        <v>-1.0695</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4568</v>
+        <v>15.7466</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4157</v>
+        <v>13.5739</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0411</v>
+        <v>2.1729</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.381</v>
+        <v>-14.8508</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-11.6087</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7143</v>
+        <v>-3.2422</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1887</v>
+        <v>-30.0033</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>26.7954</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3709</v>
+        <v>9.1297</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5879</v>
+        <v>8.0594</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2169</v>
+        <v>1.0702</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2452</v>
+        <v>-8.629000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>5.1116</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.547</v>
+        <v>-13.7406</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7548000000000006</v>
+        <v>-1.9641</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.740699999999999</v>
+        <v>-5.677499999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9858</v>
+        <v>3.7133</v>
       </c>
       <c r="G10" t="n">
         <v>11.46</v>
@@ -1234,13 +1234,13 @@
         <v>39.0609</v>
       </c>
       <c r="S10" t="n">
-        <v>9.015400000000001</v>
+        <v>7.8061</v>
       </c>
       <c r="T10" t="n">
-        <v>6.3673</v>
+        <v>3.431</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6476</v>
+        <v>4.3751</v>
       </c>
       <c r="V10" t="n">
         <v>-16.5125</v>
@@ -1267,13 +1267,13 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.713600000000001</v>
+        <v>-4.6994</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.7452</v>
+        <v>-9.2049</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0318</v>
+        <v>4.5057</v>
       </c>
       <c r="G11" t="n">
         <v>4.3398</v>
@@ -1312,13 +1312,13 @@
         <v>4.1514</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9276</v>
+        <v>1.0866</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0866</v>
+        <v>0.4539</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1589</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.8189</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.0534</v>
+        <v>-11.9581</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.562</v>
+        <v>-7.4886</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.491200000000001</v>
+        <v>-4.4695</v>
       </c>
       <c r="G12" t="n">
-        <v>1.046799999999999</v>
+        <v>-6.8271</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6448000000000007</v>
+        <v>-4.6471</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4020999999999999</v>
+        <v>-2.1798</v>
       </c>
       <c r="J12" t="n">
-        <v>13.2263</v>
+        <v>-0.0661999999999997</v>
       </c>
       <c r="K12" t="n">
-        <v>8.717700000000001</v>
+        <v>2.331999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.5088</v>
+        <v>-2.3982</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.1795</v>
+        <v>-6.760800000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.073</v>
+        <v>-6.9791</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.1065</v>
+        <v>0.2183999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-16.7943</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q12" t="n">
-        <v>-42.2688</v>
+        <v>-9.8124</v>
       </c>
       <c r="R12" t="n">
-        <v>25.4745</v>
+        <v>6.793200000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>13.501</v>
+        <v>0.6612000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>9.2555</v>
+        <v>1.1446</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2456</v>
+        <v>-0.4835999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-10.807</v>
+        <v>-2.7732</v>
       </c>
       <c r="W12" t="n">
-        <v>8.224600000000001</v>
+        <v>1.2452</v>
       </c>
       <c r="X12" t="n">
-        <v>-19.0316</v>
+        <v>-4.0184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. GOMEZ FURONES</t>
+          <t>R. CORONA NAVARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.3167</v>
+        <v>-13.4729</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.8452</v>
+        <v>-14.0683</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.4716</v>
+        <v>0.5952999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.7309</v>
+        <v>-8.3399</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8782</v>
+        <v>-2.662500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.8527</v>
+        <v>-5.6775</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.3304</v>
+        <v>0.2371000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4491999999999999</v>
+        <v>1.5869</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.779599999999999</v>
+        <v>-1.3499</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.4006</v>
+        <v>-8.5769</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3276</v>
+        <v>-4.249400000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.0733</v>
+        <v>-4.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1887000000000002</v>
+        <v>-8.114100000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8305</v>
+        <v>-18.87</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0192</v>
+        <v>10.7559</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7371</v>
+        <v>2.6982</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6844000000000001</v>
+        <v>-0.05740000000000012</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0527</v>
+        <v>2.7556</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0374</v>
+        <v>0.2828000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.622</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.0374</v>
+        <v>-4.3392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. CORONA NAVARRO</t>
+          <t>P. GOMEZ FURONES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.9896</v>
+        <v>-13.6061</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.4138</v>
+        <v>-6.396700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4243000000000003</v>
+        <v>-7.2093</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.3399</v>
+        <v>-8.7309</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.662500000000001</v>
+        <v>-1.8782</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.6775</v>
+        <v>-6.8527</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2371000000000003</v>
+        <v>-3.3304</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5869</v>
+        <v>0.4491999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3499</v>
+        <v>-3.779599999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.5769</v>
+        <v>-5.4006</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.249400000000001</v>
+        <v>-2.3276</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.3275</v>
+        <v>-3.0733</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.114100000000001</v>
+        <v>0.1887000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.87</v>
+        <v>-2.8305</v>
       </c>
       <c r="R14" t="n">
-        <v>10.7559</v>
+        <v>3.0192</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1818</v>
+        <v>-1.0264</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4029</v>
+        <v>-0.2358</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5846</v>
+        <v>-0.7905</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2828000000000001</v>
+        <v>-4.0374</v>
       </c>
       <c r="W14" t="n">
-        <v>4.622</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.3392</v>
+        <v>-4.0374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.1765</v>
+        <v>-13.6981</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.556699999999999</v>
+        <v>-23.7653</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.6201</v>
+        <v>10.0674</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.8271</v>
+        <v>-5.940700000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.6471</v>
+        <v>-2.798699999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1798</v>
+        <v>-3.142100000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0661999999999997</v>
+        <v>5.4712</v>
       </c>
       <c r="K15" t="n">
-        <v>2.331999999999999</v>
+        <v>7.410400000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.3982</v>
+        <v>-1.9395</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.760800000000001</v>
+        <v>-11.4118</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.9791</v>
+        <v>-10.2093</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2183999999999999</v>
+        <v>-1.2028</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0192</v>
+        <v>-16.0395</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.8124</v>
+        <v>-58.6857</v>
       </c>
       <c r="R15" t="n">
-        <v>6.793200000000001</v>
+        <v>42.6462</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.5571</v>
+        <v>7.7011</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9231</v>
+        <v>3.3206</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6341</v>
+        <v>4.3806</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.7732</v>
+        <v>0.581299999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2452</v>
+        <v>26.1281</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.0184</v>
+        <v>-25.5468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>V. AVINO ESPANA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.4442</v>
+        <v>-15.945</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.3077</v>
+        <v>-11.6792</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1368000000000007</v>
+        <v>-4.2658</v>
       </c>
       <c r="G16" t="n">
-        <v>-18.4064</v>
+        <v>-12.151</v>
       </c>
       <c r="H16" t="n">
-        <v>-21.0178</v>
+        <v>-2.3172</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6109</v>
+        <v>-9.833600000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.153899999999999</v>
+        <v>-8.110299999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.0709</v>
+        <v>-0.3326</v>
       </c>
       <c r="L16" t="n">
-        <v>5.9172</v>
+        <v>-7.7777</v>
       </c>
       <c r="M16" t="n">
-        <v>-14.2527</v>
+        <v>-4.0407</v>
       </c>
       <c r="N16" t="n">
-        <v>-10.9467</v>
+        <v>-1.9847</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.306100000000001</v>
+        <v>-2.056</v>
       </c>
       <c r="P16" t="n">
-        <v>4.3401</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-26.6067</v>
+        <v>-3.9627</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9468</v>
+        <v>3.3966</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8527</v>
+        <v>-1.3791</v>
       </c>
       <c r="T16" t="n">
-        <v>5.020799999999999</v>
+        <v>-0.8513999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.1681</v>
+        <v>-0.5277000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.2306</v>
+        <v>-1.8488</v>
       </c>
       <c r="W16" t="n">
-        <v>9.431900000000001</v>
+        <v>1.2452</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.6625</v>
+        <v>-3.094</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. AVINO ESPANA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-17.3505</v>
+        <v>-16.2506</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.635</v>
+        <v>-18.2701</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.7155</v>
+        <v>2.019600000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.151</v>
+        <v>-18.4064</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3172</v>
+        <v>-21.0178</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.833600000000001</v>
+        <v>2.6109</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.110299999999999</v>
+        <v>-4.153899999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3326</v>
+        <v>-10.0709</v>
       </c>
       <c r="L17" t="n">
-        <v>-7.7777</v>
+        <v>5.9172</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.0407</v>
+        <v>-14.2527</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9847</v>
+        <v>-10.9467</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.056</v>
+        <v>-3.306100000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5661</v>
+        <v>4.3401</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9627</v>
+        <v>-26.6067</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3966</v>
+        <v>30.9468</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.7847</v>
+        <v>2.0466</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.8072</v>
+        <v>3.0585</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9774</v>
+        <v>-1.0118</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8488</v>
+        <v>-4.2306</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2452</v>
+        <v>9.431900000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.094</v>
+        <v>-13.6625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-20.6078</v>
+        <v>-19.4523</v>
       </c>
       <c r="E18" t="n">
-        <v>-28.6067</v>
+        <v>-15.8039</v>
       </c>
       <c r="F18" t="n">
-        <v>7.9988</v>
+        <v>-3.648</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.940700000000001</v>
+        <v>1.046799999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.798699999999999</v>
+        <v>0.6448000000000007</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.142100000000001</v>
+        <v>0.4020999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>5.4712</v>
+        <v>13.2263</v>
       </c>
       <c r="K18" t="n">
-        <v>7.410400000000001</v>
+        <v>8.717700000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9395</v>
+        <v>4.5088</v>
       </c>
       <c r="M18" t="n">
-        <v>-11.4118</v>
+        <v>-12.1795</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.2093</v>
+        <v>-8.073</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2028</v>
+        <v>-4.1065</v>
       </c>
       <c r="P18" t="n">
-        <v>-16.0395</v>
+        <v>-16.7943</v>
       </c>
       <c r="Q18" t="n">
-        <v>-58.6857</v>
+        <v>-42.2688</v>
       </c>
       <c r="R18" t="n">
-        <v>42.6462</v>
+        <v>25.4745</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7912999999999996</v>
+        <v>7.1023</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.521</v>
+        <v>5.013599999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>2.312</v>
+        <v>2.0888</v>
       </c>
       <c r="V18" t="n">
-        <v>0.581299999999999</v>
+        <v>-10.807</v>
       </c>
       <c r="W18" t="n">
-        <v>26.1281</v>
+        <v>8.224600000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-25.5468</v>
+        <v>-19.0316</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-29.9301</v>
+        <v>-24.4523</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.9811</v>
+        <v>-14.3742</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.9494</v>
+        <v>-10.0781</v>
       </c>
       <c r="G19" t="n">
         <v>-12.1536</v>
@@ -1936,13 +1936,13 @@
         <v>15.2847</v>
       </c>
       <c r="S19" t="n">
-        <v>-9.972899999999999</v>
+        <v>-4.4952</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.0853</v>
+        <v>-0.4788</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.8875</v>
+        <v>-4.0162</v>
       </c>
       <c r="V19" t="n">
         <v>-8.747199999999999</v>
@@ -1969,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-39.0262</v>
+        <v>-26.4481</v>
       </c>
       <c r="E20" t="n">
-        <v>-39.2061</v>
+        <v>-32.4196</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1798999999999999</v>
+        <v>5.9714</v>
       </c>
       <c r="G20" t="n">
         <v>-10.8463</v>
@@ -2014,13 +2014,13 @@
         <v>27.1728</v>
       </c>
       <c r="S20" t="n">
-        <v>-16.9307</v>
+        <v>-4.3525</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.928599999999999</v>
+        <v>-2.1416</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.0022</v>
+        <v>-2.2106</v>
       </c>
       <c r="V20" t="n">
         <v>-3.3241</v>
@@ -2047,13 +2047,13 @@
         <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>-63.3122</v>
+        <v>-40.9665</v>
       </c>
       <c r="E21" t="n">
-        <v>-57.1632</v>
+        <v>-41.9755</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.1487</v>
+        <v>1.008899999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-38.1854</v>
@@ -2092,13 +2092,13 @@
         <v>45.288</v>
       </c>
       <c r="S21" t="n">
-        <v>-26.5563</v>
+        <v>-4.2103</v>
       </c>
       <c r="T21" t="n">
-        <v>-18.7875</v>
+        <v>-3.5995</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.7686</v>
+        <v>-0.6110999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>6.3358</v>
@@ -2125,16 +2125,16 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>-173.2737</v>
+        <v>-154.072</v>
       </c>
       <c r="E22" t="n">
-        <v>-175.3992</v>
+        <v>-168.7087</v>
       </c>
       <c r="F22" t="n">
-        <v>2.125200000000001</v>
+        <v>14.6371</v>
       </c>
       <c r="G22" t="n">
-        <v>-66.78710000000001</v>
+        <v>-66.7871</v>
       </c>
       <c r="H22" t="n">
         <v>-4.113300000000002</v>
@@ -2170,13 +2170,13 @@
         <v>341.3583</v>
       </c>
       <c r="S22" t="n">
-        <v>27.4922</v>
+        <v>46.694</v>
       </c>
       <c r="T22" t="n">
-        <v>17.23099999999999</v>
+        <v>23.9224</v>
       </c>
       <c r="U22" t="n">
-        <v>10.26000000000001</v>
+        <v>22.77200000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-58.87629999999999</v>
